--- a/קובץ מוצרים.xlsx
+++ b/קובץ מוצרים.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,6 +1045,36 @@
         <v>1</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2021 07 short baby.PDS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>מכנסיי בייבי מולי עם כיס</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>26 -02 overrol short slevess short panth (1).PDS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>אוברול קצר מולי</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
